--- a/per-stock/NNE/financials.xlsx
+++ b/per-stock/NNE/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1297915776</v>
+        <v>1470358016</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>730322496</v>
+        <v>901676544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-25.299492</v>
+        <v>-28.639593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -717,11 +726,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-33311692</v>
+        <v>-36838882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -732,7 +741,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52083294</v>
+        <v>52121875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -747,7 +756,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.92</v>
+        <v>28.21</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -791,6 +800,453 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D33</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C33</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B33</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B34:E34)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D9</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C9</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B9</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B9:E9)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1448,7 +1904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1474,32 +1930,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
         </is>
       </c>
     </row>
@@ -1556,19 +2012,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-12599805</v>
+        <v>-14039244</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-9716889</v>
+        <v>-12527955</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-8400323</v>
+        <v>-9966889</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>-8150323</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>-22222234</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-2811349</v>
       </c>
       <c r="G4" s="3" t="n"/>
     </row>
@@ -1579,19 +2035,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>119468</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>604662</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-203500</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-401500</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-78250</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-524250</v>
       </c>
       <c r="G5" s="3" t="n"/>
     </row>
@@ -1602,19 +2058,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>119468</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>604662</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-203500</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-401500</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-78250</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-524250</v>
       </c>
       <c r="G6" s="3" t="n"/>
     </row>
@@ -1625,19 +2081,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-21308721</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G7" s="3" t="n"/>
     </row>
@@ -1648,19 +2104,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>328963</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>291870</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>288657</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>188950</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>109237</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>63894</v>
       </c>
       <c r="G8" s="3" t="n"/>
     </row>
@@ -1671,19 +2127,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-11995143</v>
+        <v>-13919776</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-9920389</v>
+        <v>-11923293</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-8801823</v>
+        <v>-10170389</v>
       </c>
       <c r="E9" s="3" t="n">
+        <v>-8551823</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>-22300484</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-3335599</v>
       </c>
       <c r="G9" s="3" t="n"/>
     </row>
@@ -1694,19 +2150,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-12287013</v>
+        <v>-14248739</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-10209046</v>
+        <v>-12215163</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-8990773</v>
+        <v>-10459046</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>-8740773</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>-22409721</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-3399493</v>
       </c>
       <c r="G10" s="3" t="n"/>
     </row>
@@ -1717,20 +2173,20 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>4928105</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>4920707</v>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n">
         <v>1526690</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>1158251</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>789381</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>249443</v>
       </c>
     </row>
     <row r="12">
@@ -1740,20 +2196,20 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>4928105</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>4920707</v>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n">
         <v>1526690</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>1158251</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="G12" s="3" t="n">
         <v>789381</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>249443</v>
       </c>
     </row>
     <row r="13">
@@ -1763,19 +2219,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-9299634</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-7120941</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-7846910</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-7193083</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-21230471</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-2589112</v>
       </c>
       <c r="G13" s="3" t="n"/>
     </row>
@@ -1786,19 +2242,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-21308721</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G14" s="3" t="n"/>
     </row>
@@ -1809,19 +2265,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>12287013</v>
+        <v>14248739</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>10209046</v>
+        <v>12215163</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>8990773</v>
+        <v>10459046</v>
       </c>
       <c r="E15" s="3" t="n">
+        <v>8740773</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>22409721</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>3399493</v>
       </c>
       <c r="G15" s="3" t="n"/>
     </row>
@@ -1832,19 +2288,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-14072239</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-11559513</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-10412546</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-9392273</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-22487971</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-3923743</v>
       </c>
       <c r="G16" s="3" t="n"/>
     </row>
@@ -1855,19 +2311,21 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>51649161</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>49807203</v>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n">
         <v>38985143</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>37074514</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="G17" s="3" t="n">
         <v>33964495</v>
       </c>
-      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1876,19 +2334,21 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>51649161</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>49807203</v>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n">
         <v>38985143</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>37074514</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="G18" s="3" t="n">
         <v>33964495</v>
       </c>
-      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1897,19 +2357,21 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n">
         <v>-0.19</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1918,19 +2380,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n">
         <v>-0.19</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1939,19 +2403,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-21308721</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G21" s="3" t="n"/>
     </row>
@@ -1962,19 +2426,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-21308721</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G22" s="3" t="n"/>
     </row>
@@ -1985,19 +2449,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-21308721</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G23" s="3" t="n"/>
     </row>
@@ -2008,19 +2472,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-21308720</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G24" s="3" t="n"/>
     </row>
@@ -2031,19 +2495,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-21308720</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G25" s="3" t="n"/>
     </row>
@@ -2054,19 +2518,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-21308720</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-3113362</v>
       </c>
       <c r="G26" s="3" t="n"/>
     </row>
@@ -2077,19 +2541,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>850027</v>
+        <v>140468</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5632957</v>
+        <v>778177</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-130500</v>
+        <v>5882957</v>
       </c>
       <c r="E27" s="3" t="n">
+        <v>-380500</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>-57250</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-503250</v>
       </c>
       <c r="G27" s="3" t="n"/>
     </row>
@@ -2100,13 +2564,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>245365</v>
+        <v>21000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5836457</v>
+        <v>173515</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>271000</v>
+        <v>6086457</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>21000</v>
@@ -2123,19 +2587,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>176500</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>727500</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-203500</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-401500</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-78250</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-524250</v>
       </c>
       <c r="G29" s="3" t="n"/>
     </row>
@@ -2146,19 +2610,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-176500</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-727500</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>203500</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>401500</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>78250</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>524250</v>
       </c>
       <c r="G30" s="3" t="n"/>
     </row>
@@ -2169,9 +2633,11 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-57032</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-122838</v>
       </c>
-      <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
@@ -2184,20 +2650,20 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>4928105</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>4920707</v>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
         <v>1526690</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1158251</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="G32" s="3" t="n">
         <v>789381</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>249443</v>
       </c>
     </row>
     <row r="33">
@@ -2207,20 +2673,20 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>4928105</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>4920707</v>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n">
         <v>1526690</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>1158251</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>789381</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>249443</v>
       </c>
     </row>
     <row r="34">
@@ -2230,19 +2696,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-12287013</v>
+        <v>-14248739</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-10209046</v>
+        <v>-12215163</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-8990773</v>
+        <v>-10459046</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>-8740773</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>-22409721</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>-3399493</v>
       </c>
       <c r="G34" s="3" t="n"/>
     </row>
@@ -2253,19 +2719,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>12287013</v>
+        <v>14248739</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>10209046</v>
+        <v>12215163</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>8990773</v>
+        <v>10459046</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>8740773</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>22409721</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>3399493</v>
       </c>
       <c r="G35" s="3" t="n"/>
     </row>
@@ -2276,19 +2742,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>5659427</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>5400410</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>4162534</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>3666513</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>6712543</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>904923</v>
       </c>
       <c r="G36" s="3" t="n"/>
     </row>
@@ -2299,19 +2765,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>6886603</v>
+        <v>8589312</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>6046512</v>
+        <v>6814753</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5324260</v>
+        <v>6296512</v>
       </c>
       <c r="E37" s="3" t="n">
+        <v>5074260</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>15697178</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>2494570</v>
       </c>
       <c r="G37" s="3" t="n"/>
     </row>
@@ -2323,10 +2789,10 @@
       </c>
       <c r="B38" s="3" t="n"/>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
         <v>130000</v>
       </c>
-      <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
     </row>
@@ -2337,19 +2803,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6886603</v>
+        <v>8589312</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>6406512</v>
+        <v>6814753</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5194260</v>
+        <v>6656512</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>4944260</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>15697178</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2494570</v>
       </c>
       <c r="G39" s="3" t="n"/>
     </row>
@@ -2360,19 +2826,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>3586603</v>
+        <v>3389312</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6422512</v>
+        <v>3514753</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>5191660</v>
+        <v>6672512</v>
       </c>
       <c r="E40" s="3" t="n">
+        <v>4941660</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>3097178</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1694570</v>
       </c>
       <c r="G40" s="3" t="n"/>
     </row>
@@ -2383,19 +2849,21 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>3300000</v>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n">
         <v>2600</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>12600000</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="G41" s="3" t="n">
         <v>800000</v>
       </c>
-      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2448,7 +2916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3399,7 +3867,1317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>52083294</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>50581794</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>41738358</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>41538323</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>37264931</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>52083294</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>50581794</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>41738358</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>41538323</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>37264931</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2602383</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2686166</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2795542</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2807814</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2850760</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>586814143</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>590503744</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>213493683</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>217235733</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>122951445</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>595889188</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>599578789</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>222568728</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>226310778</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>132026490</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>565725580</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>576432889</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>200841189</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>209295670</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>115079880</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>586814143</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>590503744</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>213493683</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>217235733</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>122951445</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2602383</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2686166</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2795542</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2807814</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2850760</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>595889188</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>599578789</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>222568728</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>226310778</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>132026490</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>595889188</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>599578789</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>222568728</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>226310778</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>132026490</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>595889188</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>599578789</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>222568728</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>226310778</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>132026490</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>595889188</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>599578789</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>222568728</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>226310778</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>132026490</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-4790</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-10720</v>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-4790</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-10720</v>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-73197302</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-64017136</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-57500857</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-49450447</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-41855864</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>669086072</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>663601589</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>280065412</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>275757071</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>173878627</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5208</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>5056</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4173</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>4154</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3727</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5208</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5056</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4173</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>4154</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3727</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8027345</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6477372</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>6088138</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>5221434</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>6789258</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2054989</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2145365</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2261414</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2314645</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2396465</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2054989</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2145365</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2261414</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2314645</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2396465</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2054989</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2145365</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2261414</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2314645</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2396465</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5972356</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4332007</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>3826724</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2906789</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>4392793</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1250500</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1978000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1774500</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1373000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>547394</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>540801</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>534128</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>493169</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>454295</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>547394</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>540801</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>534128</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>493169</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>454295</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>4350962</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2540706</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1314596</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>639120</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2565498</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4350962</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2540706</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1314596</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>639120</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2565498</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>41667</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>4350962</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2540706</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1314596</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>597453</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2535498</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>603916533</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>606056161</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>228656866</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>231532212</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>138815748</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>32218597</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>25291265</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>23988953</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>19329753</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>19343075</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>274001</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>274001</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>269235</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>269235</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>269235</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>385500</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>435500</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>9075045</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>20484051</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>13506719</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>12344673</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>7985473</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>7998795</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-818328</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>-573963</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>-661131</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-158246</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>-49910</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>21302379</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>14080682</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>13005804</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>8143719</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>8048705</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>2722859</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1786206</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>1926656</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>2392837</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>14080682</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>13005804</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>8143719</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>8048705</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
+        <v>5325846</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>18909542</v>
+      </c>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>10149332</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>5501474</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>5325846</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>571697936</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>580764896</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>204667913</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>212202459</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>119472673</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>2802378</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2864889</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1152861</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1770084</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>922222</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>86381</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>86381</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>568895558</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>577813626</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>203265052</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>210182375</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>118550451</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>371219934</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>279677</v>
+      </c>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>197675624</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>577533949</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>203265052</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>210182375</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>118550451</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4005,13 +5783,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4020,6 +5798,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4030,25 +5809,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
@@ -4061,20 +5845,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-12570657</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-5443755</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-9556312</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-9268158</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-15079344</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-3242526</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4083,20 +5868,21 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>400000033</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>105000003</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>101400012</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4105,16 +5891,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-7306296</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-1453915</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-4647858</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-175628</v>
       </c>
-      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4123,20 +5912,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>197675624</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>577533949</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>203265052</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>210182375</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>118550451</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>123267673</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4145,20 +5935,21 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>577533949</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>203265052</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>210182375</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>118550451</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>123267673</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>28507257</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4167,14 +5958,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-5595</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-11452</v>
       </c>
-      <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4183,20 +5979,21 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-379852730</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>374280349</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>-6917323</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>91631924</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>-4717222</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>94760416</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4205,20 +6002,21 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>2853498</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>381328870</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2638989</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>100900082</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>6802122</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>101562942</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4227,20 +6025,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2853498</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>381328870</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2638989</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>100900082</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>6802122</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>101562942</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4249,20 +6048,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-21656211</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-300000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-6017700</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>-9058856</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4271,20 +6071,21 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>2803498</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>2985048</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>2938989</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>1917779</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>6802122</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>9221786</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4293,20 +6094,21 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>400000033</v>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>105000003</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" s="3" t="n">
-        <v>101400012</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4315,20 +6117,21 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>400000033</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>105000003</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>101400012</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4337,20 +6140,21 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-377441867</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-3058681</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-4647858</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-175628</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-9140891</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-3560000</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4359,20 +6163,21 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-377441867</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-3058681</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-4647858</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-175628</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-9140891</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-3560000</v>
-      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4381,12 +6186,15 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>554766</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-1604766</v>
       </c>
-      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
         <v>-3560000</v>
       </c>
     </row>
@@ -4397,14 +6205,15 @@
         </is>
       </c>
       <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="n"/>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4413,14 +6222,15 @@
         </is>
       </c>
       <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="n"/>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4429,20 +6239,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-7306296</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-1453915</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-4647858</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-175628</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-3625846</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4451,20 +6262,21 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-7306296</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-1453915</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-4647858</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-175628</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-3625846</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4473,20 +6285,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-5264361</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-3989840</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-4908454</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-9092530</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-2378453</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-3242526</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4495,20 +6308,21 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-5264361</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-3989840</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-4908454</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-9092530</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-2378453</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-3242526</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4517,20 +6331,21 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>1320599</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>918325</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>1280426</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-3067186</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>2266728</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-717308</v>
-      </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4539,20 +6354,21 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-83783</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-109376</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-12272</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-42946</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-66988</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-40335</v>
-      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4561,20 +6377,21 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>1810256</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>1226110</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>675475</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-1926378</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>1666244</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>112774</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4583,20 +6400,21 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>1810256</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>1226110</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>675475</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-1926378</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>1666244</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>112774</v>
-      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4605,20 +6423,21 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>1810256</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>1226110</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>717142</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-1938045</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>1636244</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>137774</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4627,20 +6446,21 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-492255</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-112028</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>617223</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-847862</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>667472</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-789747</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4648,15 +6468,16 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n">
         <v>-86381</v>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4664,15 +6485,16 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n">
         <v>-86381</v>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4681,20 +6503,21 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-471926</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-879284</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>203500</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>401500</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>78250</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>524250</v>
-      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4703,20 +6526,21 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>2681137</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>2072690</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1369373</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>978789</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>16476053</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4725,14 +6549,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>57032</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>122838</v>
       </c>
-      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4741,20 +6570,21 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>328963</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>291870</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>288657</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>188950</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>109237</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>63894</v>
-      </c>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4763,20 +6593,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>328963</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>291870</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>288657</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>188950</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>109237</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>63894</v>
-      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4785,20 +6616,21 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>328963</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>291870</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>288657</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>188950</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>109237</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>63894</v>
-      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4807,33 +6639,34 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-9180166</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-6516279</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-8050410</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-7594583</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-21308721</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-3113362</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4888,6 +6721,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>'Gross Profit' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
